--- a/data/trans_orig/IP07_C11_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C11_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4298</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4215</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4473</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4224</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>935</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4528</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4299</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5667</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4237</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3571</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4128</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4368</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3014</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11039</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2495</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6769</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32393</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27493</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35963</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>25857</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21804</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28723</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>31682</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>57539</t>
+          <t>59493</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51158</t>
+          <t>53296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>64407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6929</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5571</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6018</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6601</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7822</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3094</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6868</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>23,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>881</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4941</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8165</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4406</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12840</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>27,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>44,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19947</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23859</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17876</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28308</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,88%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>16709</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12156</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21277</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>57,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>41,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27781</t>
+          <t>21996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>39965</t>
+          <t>41432</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33326</t>
+          <t>34578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46368</t>
+          <t>48380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2310,107 +2310,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5393</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3855</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>4716</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -2536,74 +2536,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24410</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19778</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>26302</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>73,33%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>97,51%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>12947</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9630</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>88,99%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>66,19%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>13866</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10219</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>15567</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>65,65%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>25075</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>20967</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>26976</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>49</t>
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>38023</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33217</t>
+          <t>33555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>40947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3306</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4881</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5167</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>12020</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>23646</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>32445</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>7711</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>54700</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>48,31%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>81,45%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23725</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>12292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86397</t>
+          <t>34182</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>55208</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>43433</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>61830</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>79,53%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>62,57%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>32263</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>10864</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>55898</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>48,04%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>83,24%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>57007</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63417</t>
+          <t>37283</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>89270</t>
+          <t>87772</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49530</t>
+          <t>74296</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>97000</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>949</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>819</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>665</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>766</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>4772</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2333</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>6174</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>17,29%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>12241</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>19565</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>20,7%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>33,08%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>4093</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1790</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>8695</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>11,46%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23767</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>44411</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>36506</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>51324</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>75,09%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>61,73%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>86,78%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>27838</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>22926</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>31254</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>77,96%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>64,2%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>46808</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39633</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54176</t>
+          <t>34248</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>74646</t>
+          <t>74966</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65766</t>
+          <t>66414</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>82710</t>
+          <t>82720</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>8272</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>809</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2401</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>3372</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3574</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>11,17%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>7055</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>896</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>571</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>817</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>6476</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>32,79%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>5739</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>27072</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>21560</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>31775</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>74,13%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>59,03%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>87,0%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>23760</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>18620</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>27000</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>78,73%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>61,7%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>89,47%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>19282</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>50057</t>
+          <t>52318</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>42861</t>
+          <t>44655</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>58530</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>3567</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>8825</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>11181</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>3897</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>9042</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>5576</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>2491</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>12066</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>31962</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>58000</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>51250</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>25137</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>113552</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>54,79%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>42357</t>
+          <t>28568</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>31452</t>
+          <t>20320</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>58901</t>
+          <t>39394</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>93606</t>
+          <t>71793</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>65492</t>
+          <t>55758</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>174343</t>
+          <t>88621</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>207355</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>192758</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>221717</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>72,7%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>83,63%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>139374</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>86721</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>164424</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>41,84%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>79,34%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>210127</t>
+          <t>146903</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>193341</t>
+          <t>134769</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>222933</t>
+          <t>156297</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>349501</t>
+          <t>354257</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>272588</t>
+          <t>334280</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>376763</t>
+          <t>373057</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
